--- a/docs/data/jp/xlsx/9950.xlsx
+++ b/docs/data/jp/xlsx/9950.xlsx
@@ -2069,7 +2069,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Restaurant Business Reportable Segments</t>
+          <t>외식 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2335,7 +2335,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Wholesale Business Reportable Segments</t>
+          <t>외부 판매 사업</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -2593,7 +2593,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Retail Sales Business Reportable Segments</t>
+          <t>외부 판매 사업</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -3127,7 +3127,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Restaurant Business Segments</t>
+          <t>외식 사업</t>
         </is>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -3385,7 +3385,7 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>Retail Sales Business Segments</t>
+          <t>외부 판매 사업</t>
         </is>
       </c>
       <c r="B22" s="10" t="n"/>
@@ -9337,7 +9337,7 @@
     <row r="113">
       <c r="A113" s="18" t="inlineStr">
         <is>
-          <t>Provision For Employee Stock Ownership Plan Trust SGA</t>
+          <t>종업원 주식 급여 충당금 전입액</t>
         </is>
       </c>
       <c r="C113" s="20" t="n">
@@ -9493,7 +9493,7 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>Utilities Expenses SGA</t>
+          <t>수도광열비</t>
         </is>
       </c>
       <c r="C116" s="20" t="n">
@@ -10197,7 +10197,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>Cooperation Money Income NOI</t>
+          <t>협력금 수입</t>
         </is>
       </c>
       <c r="S129" s="20" t="n">
@@ -10826,7 +10826,7 @@
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>Reversal Of Provision For Loss On Store Closing EI</t>
+          <t>점포 폐쇄 손실 충당금 환입액</t>
         </is>
       </c>
       <c r="E143" s="20" t="n">
@@ -10873,7 +10873,7 @@
     <row r="145">
       <c r="A145" s="18" t="inlineStr">
         <is>
-          <t>Reversal Of Provision For Loss On Taking Back EI</t>
+          <t>기기 인수 손실 충당금 환입 이익</t>
         </is>
       </c>
       <c r="E145" s="20" t="n">
@@ -11165,7 +11165,7 @@
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Taking Back Equipments EL</t>
+          <t>기기 인수 손실 충당금 전입액</t>
         </is>
       </c>
       <c r="E155" s="20" t="n">
@@ -12668,7 +12668,7 @@
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>부문 · Revenues From External Customers</t>
+          <t>외식 사업 · 외부 고객 영업수익</t>
         </is>
       </c>
       <c r="E183" s="20" t="n">
@@ -12721,7 +12721,7 @@
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>부문 · Revenues From External Customers</t>
+          <t>외부 판매 사업 · 외부 고객 영업수익</t>
         </is>
       </c>
       <c r="E185" s="20" t="n">
@@ -12750,7 +12750,7 @@
     <row r="187">
       <c r="A187" s="18" t="inlineStr">
         <is>
-          <t>해외 사업 · Revenues From External Customers</t>
+          <t>해외 사업 · 외부 고객 영업수익</t>
         </is>
       </c>
       <c r="C187" s="20" t="n">
@@ -12837,7 +12837,7 @@
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · Revenues From External Customers</t>
+          <t>보고부문 합계 · 외부 고객 영업수익</t>
         </is>
       </c>
       <c r="C189" s="20" t="n">
@@ -12924,7 +12924,7 @@
     <row r="191">
       <c r="A191" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Revenues From External Customers</t>
+          <t>조정액 · 외부 고객 영업수익</t>
         </is>
       </c>
       <c r="C191" s="20" t="n">
@@ -12967,7 +12967,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>Revenues From External Customers</t>
+          <t>외부 고객 영업수익</t>
         </is>
       </c>
       <c r="C192" s="12" t="n">
@@ -13054,7 +13054,7 @@
     <row r="194">
       <c r="A194" s="18" t="inlineStr">
         <is>
-          <t>부문 · Transactions With Other Segments</t>
+          <t>외식 사업 · 부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="C194" s="20" t="n">
@@ -13070,7 +13070,7 @@
     <row r="195">
       <c r="A195" s="18" t="inlineStr">
         <is>
-          <t>부문 · Transactions With Other Segments</t>
+          <t>외부 판매 사업 · 부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="C195" s="20" t="n">
@@ -13086,7 +13086,7 @@
     <row r="196">
       <c r="A196" s="18" t="inlineStr">
         <is>
-          <t>부문 · Transactions With Other Segments</t>
+          <t>외식 사업 · 부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="E196" s="20" t="n">
@@ -13111,7 +13111,7 @@
     <row r="197">
       <c r="A197" s="18" t="inlineStr">
         <is>
-          <t>부문 · Transactions With Other Segments</t>
+          <t>외부 판매 사업 · 부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="E197" s="20" t="n">
@@ -13124,7 +13124,7 @@
     <row r="198">
       <c r="A198" s="18" t="inlineStr">
         <is>
-          <t>해외 사업 · Transactions With Other Segments</t>
+          <t>해외 사업 · 부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="C198" s="20" t="n">
@@ -13167,7 +13167,7 @@
     <row r="199">
       <c r="A199" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · Transactions With Other Segments</t>
+          <t>보고부문 합계 · 부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="C199" s="20" t="n">
@@ -13210,7 +13210,7 @@
     <row r="200">
       <c r="A200" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Transactions With Other Segments</t>
+          <t>조정액 · 부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="C200" s="20" t="n">
@@ -13253,7 +13253,7 @@
     <row r="201">
       <c r="A201" s="18" t="inlineStr">
         <is>
-          <t>Transactions With Other Segments</t>
+          <t>부문 간 내부 영업수익 또는 대체액</t>
         </is>
       </c>
       <c r="C201" s="20" t="n">
@@ -13296,7 +13296,7 @@
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>외식 사업 · 계</t>
         </is>
       </c>
       <c r="C202" s="20" t="n">
@@ -13332,7 +13332,7 @@
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>외부 판매 사업 · 계</t>
         </is>
       </c>
       <c r="C204" s="20" t="n">
@@ -13368,7 +13368,7 @@
     <row r="206">
       <c r="A206" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>외식 사업 · 계</t>
         </is>
       </c>
       <c r="E206" s="20" t="n">
@@ -13421,7 +13421,7 @@
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>외부 판매 사업 · 계</t>
         </is>
       </c>
       <c r="E208" s="20" t="n">
@@ -13754,7 +13754,7 @@
     <row r="217">
       <c r="A217" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>외식 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C217" s="20" t="n">
@@ -13770,7 +13770,7 @@
     <row r="218">
       <c r="A218" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>외부 판매 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C218" s="20" t="n">
@@ -13786,7 +13786,7 @@
     <row r="219">
       <c r="A219" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>외식 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="E219" s="20" t="n">
@@ -13811,7 +13811,7 @@
     <row r="220">
       <c r="A220" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>외부 판매 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="E220" s="20" t="n">
@@ -14040,7 +14040,7 @@
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
         <is>
-          <t>부문 · Revenues From External Customers</t>
+          <t>외식 사업 · 외부 고객 영업수익</t>
         </is>
       </c>
       <c r="C226" s="20" t="n">
@@ -14076,7 +14076,7 @@
     <row r="228">
       <c r="A228" s="18" t="inlineStr">
         <is>
-          <t>부문 · Revenues From External Customers</t>
+          <t>외부 판매 사업 · 외부 고객 영업수익</t>
         </is>
       </c>
       <c r="C228" s="20" t="n">
@@ -14847,7 +14847,7 @@
     <row r="248">
       <c r="A248" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Loss On Taking Back Equipments Ope CF</t>
+          <t>기기 인수 손실 충당금 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="F248" s="20" t="n">
@@ -15006,7 +15006,7 @@
     <row r="254">
       <c r="A254" s="18" t="inlineStr">
         <is>
-          <t>Cooperation Money Income Ope CF</t>
+          <t>협력금 수입</t>
         </is>
       </c>
       <c r="F254" s="20" t="n">
@@ -15759,7 +15759,7 @@
     <row r="275">
       <c r="A275" s="18" t="inlineStr">
         <is>
-          <t>Cooperation Money Income Received Ope CF</t>
+          <t>협력금 수취액</t>
         </is>
       </c>
       <c r="F275" s="20" t="n">
@@ -20568,7 +20568,7 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Taking Back Equipments CL</t>
+          <t>기기 인수 손실 충당금</t>
         </is>
       </c>
       <c r="I109" s="20" t="n">
